--- a/docentes/Rodríguez Román Leticia - Estadisticos 20211.xlsx
+++ b/docentes/Rodríguez Román Leticia - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="60">
   <si>
     <t>Mat</t>
   </si>
@@ -76,163 +76,127 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>LARRINAGA</t>
+  </si>
+  <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>NUBE</t>
+  </si>
+  <si>
     <t>ADELL</t>
   </si>
   <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
-    <t>PONCE</t>
-  </si>
-  <si>
-    <t>HUESCA</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>CANSECO</t>
+  </si>
+  <si>
+    <t>MATA</t>
+  </si>
+  <si>
+    <t>QUIRIZ</t>
   </si>
   <si>
     <t>ANASTACIO</t>
   </si>
   <si>
-    <t>ESPIRITU</t>
-  </si>
-  <si>
-    <t>ROMAN</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>CANSECO</t>
-  </si>
-  <si>
-    <t>MATA</t>
-  </si>
-  <si>
-    <t>QUIRIZ</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
     <t>CID</t>
   </si>
   <si>
-    <t>VALENTE</t>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>SANTES</t>
+  </si>
+  <si>
+    <t>CONCHE</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>ALEMAN</t>
   </si>
   <si>
     <t>AGUILAR</t>
   </si>
   <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>VICTORIANO</t>
+    <t>GALEOTE</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>LEAL</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
   </si>
   <si>
     <t>ROMERO</t>
   </si>
   <si>
-    <t>TEQUIHUATLE</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>GALEOTE</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>LEAL</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
     <t>VALENCIA</t>
   </si>
   <si>
-    <t>GAMEZ</t>
+    <t>SEGURA</t>
+  </si>
+  <si>
+    <t>GONZALO FEDERICO</t>
+  </si>
+  <si>
+    <t>GUSTAVO</t>
+  </si>
+  <si>
+    <t>YAHIR</t>
+  </si>
+  <si>
+    <t>CHRISTIAN YAIR</t>
   </si>
   <si>
     <t>CRISTOPHER ALAIN</t>
   </si>
   <si>
-    <t>JAIR</t>
-  </si>
-  <si>
-    <t>ALETHIA LUCIA</t>
-  </si>
-  <si>
-    <t>ALDAIR OMAR</t>
-  </si>
-  <si>
-    <t>MARIAN</t>
+    <t>GERMAN ISAI</t>
+  </si>
+  <si>
+    <t>DIEGO</t>
+  </si>
+  <si>
+    <t>DINA BERENICE</t>
+  </si>
+  <si>
+    <t>ANGELA</t>
+  </si>
+  <si>
+    <t>CRISTIAN ARTURO</t>
+  </si>
+  <si>
+    <t>MONICA</t>
   </si>
   <si>
     <t>HIRAM FABIAN</t>
   </si>
   <si>
-    <t>ALEJANDRO</t>
-  </si>
-  <si>
-    <t>IGNACIO</t>
-  </si>
-  <si>
-    <t>LUIS ALEJANDRO</t>
-  </si>
-  <si>
-    <t>JOSE ANTONIO</t>
-  </si>
-  <si>
-    <t>FERNANDA</t>
-  </si>
-  <si>
-    <t>GERMAN ISAI</t>
-  </si>
-  <si>
-    <t>DINA BERENICE</t>
-  </si>
-  <si>
-    <t>ANGELA</t>
-  </si>
-  <si>
-    <t>CRISTIAN ARTURO</t>
-  </si>
-  <si>
-    <t>MONICA</t>
-  </si>
-  <si>
-    <t>BERENICE</t>
-  </si>
-  <si>
     <t>JESUS</t>
   </si>
   <si>
-    <t>ABIUD</t>
+    <t>CESAR</t>
   </si>
 </sst>
 </file>
@@ -633,19 +597,19 @@
         <v>36</v>
       </c>
       <c r="D2">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F2">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="G2">
-        <v>33.33</v>
+        <v>58.33</v>
       </c>
       <c r="H2">
-        <v>7.1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -659,19 +623,19 @@
         <v>39</v>
       </c>
       <c r="D3">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F3">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G3">
-        <v>69.23</v>
+        <v>74.36</v>
       </c>
       <c r="H3">
-        <v>7.6</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -685,19 +649,19 @@
         <v>36</v>
       </c>
       <c r="D4">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F4">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="G4">
-        <v>52.78</v>
+        <v>66.67</v>
       </c>
       <c r="H4">
-        <v>7.7</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -711,19 +675,19 @@
         <v>32</v>
       </c>
       <c r="D5">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F5">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="G5">
-        <v>53.13</v>
+        <v>68.75</v>
       </c>
       <c r="H5">
-        <v>7.1</v>
+        <v>6.3</v>
       </c>
     </row>
   </sheetData>
@@ -776,16 +740,19 @@
         <v>36</v>
       </c>
       <c r="D2">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="E2">
+        <v>24</v>
+      </c>
+      <c r="F2">
         <v>12</v>
       </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
       <c r="G2">
-        <v>0</v>
+        <v>33.33</v>
+      </c>
+      <c r="H2">
+        <v>6.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -799,16 +766,19 @@
         <v>39</v>
       </c>
       <c r="D3">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="E3">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>58.97</v>
+      </c>
+      <c r="H3">
+        <v>7.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -822,16 +792,19 @@
         <v>36</v>
       </c>
       <c r="D4">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="E4">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>38.89</v>
+      </c>
+      <c r="H4">
+        <v>7.9</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -845,16 +818,19 @@
         <v>32</v>
       </c>
       <c r="D5">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="E5">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>65.63</v>
+      </c>
+      <c r="H5">
+        <v>6.6</v>
       </c>
     </row>
   </sheetData>
@@ -907,19 +883,19 @@
         <v>36</v>
       </c>
       <c r="D2">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F2">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="G2">
-        <v>33.33</v>
+        <v>58.33</v>
       </c>
       <c r="H2">
-        <v>7.1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -933,19 +909,19 @@
         <v>39</v>
       </c>
       <c r="D3">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F3">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G3">
-        <v>69.23</v>
+        <v>74.36</v>
       </c>
       <c r="H3">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -959,19 +935,19 @@
         <v>36</v>
       </c>
       <c r="D4">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F4">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="G4">
-        <v>52.78</v>
+        <v>66.67</v>
       </c>
       <c r="H4">
-        <v>7.7</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -985,19 +961,19 @@
         <v>32</v>
       </c>
       <c r="D5">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F5">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="G5">
-        <v>53.13</v>
+        <v>68.75</v>
       </c>
       <c r="H5">
-        <v>7.1</v>
+        <v>6.4</v>
       </c>
     </row>
   </sheetData>
@@ -1007,7 +983,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1039,439 +1015,324 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920002</v>
+        <v>20330051920234</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D2" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G2">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920361</v>
+        <v>20330051920039</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G3">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920245</v>
+        <v>20330051920050</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D4" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G4">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920168</v>
+        <v>20330051920100</v>
       </c>
       <c r="B5" t="s">
         <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D5" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G5">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920184</v>
+        <v>20330051920002</v>
       </c>
       <c r="B6" t="s">
         <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D6" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G6">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920042</v>
+        <v>20330051920228</v>
       </c>
       <c r="B7" t="s">
         <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D7" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G7">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920011</v>
+        <v>20330051920240</v>
       </c>
       <c r="B8" t="s">
         <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D8" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G8">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920012</v>
+        <v>20330051920158</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D9" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G9">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920027</v>
+        <v>20330051920161</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D10" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G10">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920036</v>
+        <v>20330051920172</v>
       </c>
       <c r="B11" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" t="s">
         <v>27</v>
       </c>
-      <c r="C11" t="s">
-        <v>45</v>
-      </c>
       <c r="D11" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G11">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920224</v>
+        <v>20330051920178</v>
       </c>
       <c r="B12" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C12" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D12" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G12">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920228</v>
+        <v>20330051920042</v>
       </c>
       <c r="B13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C13" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D13" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G13">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>20330051920158</v>
+        <v>20330051920046</v>
       </c>
       <c r="B14" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C14" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D14" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G14">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>20330051920161</v>
+        <v>20330051920052</v>
       </c>
       <c r="B15" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C15" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D15" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G15">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>20330051920172</v>
-      </c>
-      <c r="B16" t="s">
-        <v>32</v>
-      </c>
-      <c r="C16" t="s">
-        <v>31</v>
-      </c>
-      <c r="D16" t="s">
-        <v>67</v>
-      </c>
-      <c r="E16" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" t="s">
-        <v>11</v>
-      </c>
-      <c r="G16">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>20330051920178</v>
-      </c>
-      <c r="B17" t="s">
-        <v>33</v>
-      </c>
-      <c r="C17" t="s">
-        <v>50</v>
-      </c>
-      <c r="D17" t="s">
-        <v>68</v>
-      </c>
-      <c r="E17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" t="s">
-        <v>11</v>
-      </c>
-      <c r="G17">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>20330051920254</v>
-      </c>
-      <c r="B18" t="s">
-        <v>34</v>
-      </c>
-      <c r="C18" t="s">
-        <v>42</v>
-      </c>
-      <c r="D18" t="s">
-        <v>69</v>
-      </c>
-      <c r="E18" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" t="s">
-        <v>11</v>
-      </c>
-      <c r="G18">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>20330051920046</v>
-      </c>
-      <c r="B19" t="s">
-        <v>35</v>
-      </c>
-      <c r="C19" t="s">
-        <v>51</v>
-      </c>
-      <c r="D19" t="s">
-        <v>70</v>
-      </c>
-      <c r="E19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" t="s">
-        <v>12</v>
-      </c>
-      <c r="G19">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>20330051920111</v>
-      </c>
-      <c r="B20" t="s">
-        <v>36</v>
-      </c>
-      <c r="C20" t="s">
-        <v>52</v>
-      </c>
-      <c r="D20" t="s">
-        <v>71</v>
-      </c>
-      <c r="E20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" t="s">
-        <v>12</v>
-      </c>
-      <c r="G20">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Rodríguez Román Leticia - Estadisticos 20211.xlsx
+++ b/docentes/Rodríguez Román Leticia - Estadisticos 20211.xlsx
@@ -1194,7 +1194,7 @@
         <v>11</v>
       </c>
       <c r="G9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -1217,7 +1217,7 @@
         <v>11</v>
       </c>
       <c r="G10">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -1240,7 +1240,7 @@
         <v>11</v>
       </c>
       <c r="G11">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:7">

--- a/docentes/Rodríguez Román Leticia - Estadisticos 20211.xlsx
+++ b/docentes/Rodríguez Román Leticia - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="63">
   <si>
     <t>Mat</t>
   </si>
@@ -91,6 +91,9 @@
     <t>ADELL</t>
   </si>
   <si>
+    <t>XOCUA</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
@@ -133,6 +136,9 @@
     <t>AGUILAR</t>
   </si>
   <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
     <t>GALEOTE</t>
   </si>
   <si>
@@ -170,6 +176,9 @@
   </si>
   <si>
     <t>CRISTOPHER ALAIN</t>
+  </si>
+  <si>
+    <t>MARCOS URIEL</t>
   </si>
   <si>
     <t>GERMAN ISAI</t>
@@ -766,16 +775,16 @@
         <v>39</v>
       </c>
       <c r="D3">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E3">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G3">
-        <v>58.97</v>
+        <v>61.54</v>
       </c>
       <c r="H3">
         <v>7.5</v>
@@ -792,19 +801,19 @@
         <v>36</v>
       </c>
       <c r="D4">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E4">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F4">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G4">
-        <v>38.89</v>
+        <v>44.44</v>
       </c>
       <c r="H4">
-        <v>7.9</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -983,7 +992,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1021,10 +1030,10 @@
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1044,10 +1053,10 @@
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1067,10 +1076,10 @@
         <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1090,10 +1099,10 @@
         <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1113,10 +1122,10 @@
         <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D6" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1125,27 +1134,27 @@
         <v>9</v>
       </c>
       <c r="G6">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920228</v>
+        <v>20330051920035</v>
       </c>
       <c r="B7" t="s">
         <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D7" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1153,16 +1162,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920240</v>
+        <v>20330051920228</v>
       </c>
       <c r="B8" t="s">
         <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D8" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1171,44 +1180,44 @@
         <v>10</v>
       </c>
       <c r="G8">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920158</v>
+        <v>20330051920240</v>
       </c>
       <c r="B9" t="s">
         <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D9" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920161</v>
+        <v>20330051920158</v>
       </c>
       <c r="B10" t="s">
         <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D10" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1217,21 +1226,21 @@
         <v>11</v>
       </c>
       <c r="G10">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920172</v>
+        <v>20330051920161</v>
       </c>
       <c r="B11" t="s">
         <v>28</v>
       </c>
       <c r="C11" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="D11" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1245,16 +1254,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920178</v>
+        <v>20330051920172</v>
       </c>
       <c r="B12" t="s">
         <v>29</v>
       </c>
       <c r="C12" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="D12" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1263,44 +1272,44 @@
         <v>11</v>
       </c>
       <c r="G12">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920042</v>
+        <v>20330051920178</v>
       </c>
       <c r="B13" t="s">
         <v>30</v>
       </c>
       <c r="C13" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D13" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G13">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>20330051920046</v>
+        <v>20330051920042</v>
       </c>
       <c r="B14" t="s">
         <v>31</v>
       </c>
       <c r="C14" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D14" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1309,21 +1318,21 @@
         <v>12</v>
       </c>
       <c r="G14">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>20330051920052</v>
+        <v>20330051920046</v>
       </c>
       <c r="B15" t="s">
         <v>32</v>
       </c>
       <c r="C15" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D15" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -1332,6 +1341,29 @@
         <v>12</v>
       </c>
       <c r="G15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>20330051920052</v>
+      </c>
+      <c r="B16" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16" t="s">
+        <v>47</v>
+      </c>
+      <c r="D16" t="s">
+        <v>62</v>
+      </c>
+      <c r="E16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" t="s">
+        <v>12</v>
+      </c>
+      <c r="G16">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Rodríguez Román Leticia - Estadisticos 20211.xlsx
+++ b/docentes/Rodríguez Román Leticia - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="66">
   <si>
     <t>Mat</t>
   </si>
@@ -76,6 +76,9 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>NICIO</t>
+  </si>
+  <si>
     <t>LARRINAGA</t>
   </si>
   <si>
@@ -121,6 +124,9 @@
     <t>FLORES</t>
   </si>
   <si>
+    <t>MORALES</t>
+  </si>
+  <si>
     <t>SANTES</t>
   </si>
   <si>
@@ -161,6 +167,9 @@
   </si>
   <si>
     <t>SEGURA</t>
+  </si>
+  <si>
+    <t>JOSE JULIAN</t>
   </si>
   <si>
     <t>GONZALO FEDERICO</t>
@@ -992,7 +1001,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1024,22 +1033,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920234</v>
+        <v>20330051920025</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1047,22 +1056,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920039</v>
+        <v>20330051920234</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1070,16 +1079,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920050</v>
+        <v>20330051920039</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D4" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1093,16 +1102,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920100</v>
+        <v>20330051920050</v>
       </c>
       <c r="B5" t="s">
         <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D5" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1116,22 +1125,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920002</v>
+        <v>20330051920100</v>
       </c>
       <c r="B6" t="s">
         <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D6" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1139,16 +1148,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920035</v>
+        <v>20330051920002</v>
       </c>
       <c r="B7" t="s">
         <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D7" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1162,22 +1171,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920228</v>
+        <v>20330051920035</v>
       </c>
       <c r="B8" t="s">
         <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D8" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1185,16 +1194,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920240</v>
+        <v>20330051920228</v>
       </c>
       <c r="B9" t="s">
         <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D9" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1203,44 +1212,44 @@
         <v>10</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920158</v>
+        <v>20330051920240</v>
       </c>
       <c r="B10" t="s">
         <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D10" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G10">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920161</v>
+        <v>20330051920158</v>
       </c>
       <c r="B11" t="s">
         <v>28</v>
       </c>
       <c r="C11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D11" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1249,21 +1258,21 @@
         <v>11</v>
       </c>
       <c r="G11">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920172</v>
+        <v>20330051920161</v>
       </c>
       <c r="B12" t="s">
         <v>29</v>
       </c>
       <c r="C12" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="D12" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1277,16 +1286,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920178</v>
+        <v>20330051920172</v>
       </c>
       <c r="B13" t="s">
         <v>30</v>
       </c>
       <c r="C13" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="D13" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1295,44 +1304,44 @@
         <v>11</v>
       </c>
       <c r="G13">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>20330051920042</v>
+        <v>20330051920178</v>
       </c>
       <c r="B14" t="s">
         <v>31</v>
       </c>
       <c r="C14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D14" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G14">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>20330051920046</v>
+        <v>20330051920042</v>
       </c>
       <c r="B15" t="s">
         <v>32</v>
       </c>
       <c r="C15" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D15" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -1346,16 +1355,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>20330051920052</v>
+        <v>20330051920046</v>
       </c>
       <c r="B16" t="s">
         <v>33</v>
       </c>
       <c r="C16" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D16" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -1364,6 +1373,29 @@
         <v>12</v>
       </c>
       <c r="G16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>20330051920052</v>
+      </c>
+      <c r="B17" t="s">
+        <v>34</v>
+      </c>
+      <c r="C17" t="s">
+        <v>49</v>
+      </c>
+      <c r="D17" t="s">
+        <v>65</v>
+      </c>
+      <c r="E17" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G17">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Rodríguez Román Leticia - Estadisticos 20211.xlsx
+++ b/docentes/Rodríguez Román Leticia - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="57">
   <si>
     <t>Mat</t>
   </si>
@@ -76,40 +76,34 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>NICIO</t>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>PLIEGO</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>NUBE</t>
+  </si>
+  <si>
+    <t>TELLEZ</t>
   </si>
   <si>
     <t>LARRINAGA</t>
   </si>
   <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>NUBE</t>
-  </si>
-  <si>
-    <t>ADELL</t>
-  </si>
-  <si>
-    <t>XOCUA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
     <t>BAUTISTA</t>
   </si>
   <si>
-    <t>CANSECO</t>
-  </si>
-  <si>
-    <t>MATA</t>
+    <t>CARRERA</t>
   </si>
   <si>
     <t>QUIRIZ</t>
@@ -118,43 +112,37 @@
     <t>ANASTACIO</t>
   </si>
   <si>
-    <t>CID</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>MORALES</t>
+    <t>MENDIZABAL</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>GALEOTE</t>
+  </si>
+  <si>
+    <t>LORENZO</t>
+  </si>
+  <si>
+    <t>TEPEPA</t>
+  </si>
+  <si>
+    <t>ALEMAN</t>
+  </si>
+  <si>
+    <t>VALENCIA</t>
   </si>
   <si>
     <t>SANTES</t>
   </si>
   <si>
-    <t>CONCHE</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>ALEMAN</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>GALEOTE</t>
-  </si>
-  <si>
     <t>LOPEZ</t>
   </si>
   <si>
     <t>DIAZ</t>
   </si>
   <si>
-    <t>LEAL</t>
+    <t>TINOCO</t>
   </si>
   <si>
     <t>RAMOS</t>
@@ -163,46 +151,34 @@
     <t>ROMERO</t>
   </si>
   <si>
-    <t>VALENCIA</t>
-  </si>
-  <si>
-    <t>SEGURA</t>
-  </si>
-  <si>
-    <t>JOSE JULIAN</t>
+    <t>LUIS ANGEL</t>
+  </si>
+  <si>
+    <t>GERMAN ISAI</t>
+  </si>
+  <si>
+    <t>VICTOR GAMALIEL</t>
+  </si>
+  <si>
+    <t>ELELYN IVETH</t>
+  </si>
+  <si>
+    <t>CHRISTIAN YAIR</t>
+  </si>
+  <si>
+    <t>BENY ALEXANDER</t>
   </si>
   <si>
     <t>GONZALO FEDERICO</t>
   </si>
   <si>
-    <t>GUSTAVO</t>
-  </si>
-  <si>
-    <t>YAHIR</t>
-  </si>
-  <si>
-    <t>CHRISTIAN YAIR</t>
-  </si>
-  <si>
-    <t>CRISTOPHER ALAIN</t>
-  </si>
-  <si>
-    <t>MARCOS URIEL</t>
-  </si>
-  <si>
-    <t>GERMAN ISAI</t>
-  </si>
-  <si>
     <t>DIEGO</t>
   </si>
   <si>
     <t>DINA BERENICE</t>
   </si>
   <si>
-    <t>ANGELA</t>
-  </si>
-  <si>
-    <t>CRISTIAN ARTURO</t>
+    <t>ANGELES NAHOMI</t>
   </si>
   <si>
     <t>MONICA</t>
@@ -211,10 +187,7 @@
     <t>HIRAM FABIAN</t>
   </si>
   <si>
-    <t>JESUS</t>
-  </si>
-  <si>
-    <t>CESAR</t>
+    <t>ALDER ALBERTO</t>
   </si>
 </sst>
 </file>
@@ -758,19 +731,19 @@
         <v>36</v>
       </c>
       <c r="D2">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F2">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G2">
-        <v>33.33</v>
+        <v>50</v>
       </c>
       <c r="H2">
-        <v>6.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -784,19 +757,19 @@
         <v>39</v>
       </c>
       <c r="D3">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F3">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G3">
-        <v>61.54</v>
+        <v>71.79000000000001</v>
       </c>
       <c r="H3">
-        <v>7.5</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -810,19 +783,19 @@
         <v>36</v>
       </c>
       <c r="D4">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F4">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G4">
-        <v>44.44</v>
+        <v>58.33</v>
       </c>
       <c r="H4">
-        <v>7.5</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -836,19 +809,19 @@
         <v>32</v>
       </c>
       <c r="D5">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F5">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G5">
-        <v>65.63</v>
+        <v>68.75</v>
       </c>
       <c r="H5">
-        <v>6.6</v>
+        <v>6.3</v>
       </c>
     </row>
   </sheetData>
@@ -904,16 +877,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G2">
-        <v>58.33</v>
+        <v>61.11</v>
       </c>
       <c r="H2">
-        <v>6</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -930,16 +903,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F3">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G3">
-        <v>74.36</v>
+        <v>71.79000000000001</v>
       </c>
       <c r="H3">
-        <v>6.8</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -956,16 +929,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F4">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G4">
-        <v>66.67</v>
+        <v>69.44</v>
       </c>
       <c r="H4">
-        <v>6.6</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -982,16 +955,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="G5">
-        <v>68.75</v>
+        <v>87.5</v>
       </c>
       <c r="H5">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
     </row>
   </sheetData>
@@ -1001,7 +974,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1033,16 +1006,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920025</v>
+        <v>20330051920013</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D2" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1056,16 +1029,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920234</v>
+        <v>20330051920228</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D3" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1079,22 +1052,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920039</v>
+        <v>20330051920244</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D4" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1102,22 +1075,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920050</v>
+        <v>20330051920183</v>
       </c>
       <c r="B5" t="s">
         <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D5" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1131,10 +1104,10 @@
         <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D6" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1148,22 +1121,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920002</v>
+        <v>20330051920109</v>
       </c>
       <c r="B7" t="s">
         <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D7" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1171,39 +1144,39 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920035</v>
+        <v>20330051920234</v>
       </c>
       <c r="B8" t="s">
         <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D8" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920228</v>
+        <v>20330051920240</v>
       </c>
       <c r="B9" t="s">
         <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D9" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1212,27 +1185,27 @@
         <v>10</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920240</v>
+        <v>20330051920158</v>
       </c>
       <c r="B10" t="s">
         <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D10" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -1240,16 +1213,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920158</v>
+        <v>20330051920162</v>
       </c>
       <c r="B11" t="s">
         <v>28</v>
       </c>
       <c r="C11" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D11" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1258,21 +1231,21 @@
         <v>11</v>
       </c>
       <c r="G11">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920161</v>
+        <v>20330051920178</v>
       </c>
       <c r="B12" t="s">
         <v>29</v>
       </c>
       <c r="C12" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D12" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1286,22 +1259,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920172</v>
+        <v>20330051920042</v>
       </c>
       <c r="B13" t="s">
         <v>30</v>
       </c>
       <c r="C13" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="D13" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -1309,93 +1282,21 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>20330051920178</v>
+        <v>20330051920099</v>
       </c>
       <c r="B14" t="s">
         <v>31</v>
       </c>
-      <c r="C14" t="s">
-        <v>46</v>
-      </c>
       <c r="D14" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G14">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>20330051920042</v>
-      </c>
-      <c r="B15" t="s">
-        <v>32</v>
-      </c>
-      <c r="C15" t="s">
-        <v>47</v>
-      </c>
-      <c r="D15" t="s">
-        <v>63</v>
-      </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s">
-        <v>12</v>
-      </c>
-      <c r="G15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>20330051920046</v>
-      </c>
-      <c r="B16" t="s">
-        <v>33</v>
-      </c>
-      <c r="C16" t="s">
-        <v>48</v>
-      </c>
-      <c r="D16" t="s">
-        <v>64</v>
-      </c>
-      <c r="E16" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" t="s">
-        <v>12</v>
-      </c>
-      <c r="G16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>20330051920052</v>
-      </c>
-      <c r="B17" t="s">
-        <v>34</v>
-      </c>
-      <c r="C17" t="s">
-        <v>49</v>
-      </c>
-      <c r="D17" t="s">
-        <v>65</v>
-      </c>
-      <c r="E17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G17">
         <v>1</v>
       </c>
     </row>
